--- a/TestData/LV_TMTT0011413_VerifyTimeEntriesRoundOffForSupervisorInTimeRecordManagerLightningView.xlsx
+++ b/TestData/LV_TMTT0011413_VerifyTimeEntriesRoundOffForSupervisorInTimeRecordManagerLightningView.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6325D4D4-B0ED-46F8-8524-06761E1D26EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE4DA40A-016C-4B66-BFB0-2BEC1312791A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
